--- a/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
@@ -396,13 +396,13 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C8">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
@@ -402,7 +402,7 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -421,7 +421,7 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -434,13 +434,13 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C8">
-        <v>308</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">

--- a/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
+++ b/01_analyses_states/Delhi/results/SoIB_summaries.xlsx
@@ -393,16 +393,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>46.2</v>
       </c>
       <c r="E2">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -415,13 +415,13 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>7.7</v>
       </c>
       <c r="E3">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -431,16 +431,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="E4">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
@@ -469,13 +469,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>75</v>
+        <v>7.7</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -488,10 +488,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="C8">
-        <v>301</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>286</v>
+        <v>387</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>553</v>
+        <v>441</v>
       </c>
     </row>
   </sheetData>
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -763,13 +763,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>69.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="D2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E2">
         <v>75.8</v>
@@ -782,13 +782,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C3">
-        <v>30.1</v>
+        <v>27.2</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
         <v>24.2</v>
